--- a/All_Code/Q2/Results/Tables/interval_template_mapping.xlsx
+++ b/All_Code/Q2/Results/Tables/interval_template_mapping.xlsx
@@ -449,11 +449,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0:10-0:20</t>
+          <t>0:00-0:10+1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
@@ -467,11 +467,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0:20-0:30</t>
+          <t>0:10-0:20</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -485,11 +485,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0:30-0:40</t>
+          <t>0:20-0:30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -503,11 +503,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0:40-0:50</t>
+          <t>0:30-0:40</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -521,11 +521,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0:50-1:00</t>
+          <t>0:40-0:50</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -539,11 +539,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1:00-1:10</t>
+          <t>0:50-1:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -557,11 +557,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1:10-1:20</t>
+          <t>1:00-1:10</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -575,11 +575,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1:20-1:30</t>
+          <t>1:10-1:20</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -593,11 +593,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1:30-1:40</t>
+          <t>1:20-1:30</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -611,11 +611,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1:40-1:50</t>
+          <t>1:30-1:40</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -629,11 +629,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1:50-2:00</t>
+          <t>1:40-1:50</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -647,11 +647,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2:00-2:10</t>
+          <t>1:50-2:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -665,11 +665,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2:10-2:20</t>
+          <t>2:00-2:10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -683,11 +683,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2:20-2:30</t>
+          <t>2:10-2:20</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -701,11 +701,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2:30-2:40</t>
+          <t>2:20-2:30</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -719,11 +719,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2:40-2:50</t>
+          <t>2:30-2:40</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -737,11 +737,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2:50-3:00</t>
+          <t>2:40-2:50</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -755,11 +755,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3:00-3:10</t>
+          <t>2:50-3:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -773,11 +773,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3:10-3:20</t>
+          <t>3:00-3:10</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -791,11 +791,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3:20-3:30</t>
+          <t>3:10-3:20</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -809,11 +809,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3:30-3:40</t>
+          <t>3:20-3:30</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -827,11 +827,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3:40-3:50</t>
+          <t>3:30-3:40</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -845,11 +845,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3:50-4:00</t>
+          <t>3:40-3:50</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -863,11 +863,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4:00-4:10</t>
+          <t>3:50-4:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -881,11 +881,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4:10-4:20</t>
+          <t>4:00-4:10</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -899,11 +899,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4:20-4:30</t>
+          <t>4:10-4:20</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -917,11 +917,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4:30-4:40</t>
+          <t>4:20-4:30</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -935,11 +935,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4:40-4:50</t>
+          <t>4:30-4:40</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -953,11 +953,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4:50-5:00</t>
+          <t>4:40-4:50</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -971,11 +971,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5:00-5:10</t>
+          <t>4:50-5:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -989,11 +989,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5:10-5:20</t>
+          <t>5:00-5:10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5:20-5:30</t>
+          <t>5:10-5:20</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -1025,11 +1025,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5:30-5:40</t>
+          <t>5:20-5:30</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5:40-5:50</t>
+          <t>5:30-5:40</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -1061,11 +1061,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5:50-6:00</t>
+          <t>5:40-5:50</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -1079,11 +1079,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6:00-6:10</t>
+          <t>5:50-6:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6:10-6:20</t>
+          <t>6:00-6:10</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6:20-6:30</t>
+          <t>6:10-6:20</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6:30-6:40</t>
+          <t>6:20-6:30</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6:40-6:50</t>
+          <t>6:30-6:40</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1169,11 +1169,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6:50-7:00</t>
+          <t>6:40-6:50</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -1187,11 +1187,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7:0-7:10</t>
+          <t>6:50-7:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -1205,11 +1205,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7:10-7:20</t>
+          <t>7:0-7:10</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -1223,11 +1223,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7:20-7:30</t>
+          <t>7:10-7:20</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -1241,11 +1241,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7:30-7:40</t>
+          <t>7:20-7:30</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7:40-7:50</t>
+          <t>7:30-7:40</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -1277,11 +1277,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7:50-8:00</t>
+          <t>7:40-7:50</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
@@ -1295,11 +1295,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8:00-8:10</t>
+          <t>7:50-8:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8:10-8:20</t>
+          <t>8:00-8:10</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -1331,11 +1331,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>8:20-8:30</t>
+          <t>8:10-8:20</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8:30-8:40</t>
+          <t>8:20-8:30</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53">
@@ -1367,11 +1367,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8:40-8:50</t>
+          <t>8:30-8:40</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8:50-9:00</t>
+          <t>8:40-8:50</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9:00-9:10</t>
+          <t>8:50-9:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56">
@@ -1421,11 +1421,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9:10-9:20</t>
+          <t>9:00-9:10</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
@@ -1439,11 +1439,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9:20-9:30</t>
+          <t>9:10-9:20</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
@@ -1457,11 +1457,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9:30-9:40</t>
+          <t>9:20-9:30</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9:40-9:50</t>
+          <t>9:30-9:40</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9:50-10:00</t>
+          <t>9:40-9:50</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10:00-10:10</t>
+          <t>9:50-10:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>10:10-10:20</t>
+          <t>10:00-10:10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63">
@@ -1547,11 +1547,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10:20-10:30</t>
+          <t>10:10-10:20</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -1565,11 +1565,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>10:30-10:40</t>
+          <t>10:20-10:30</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
@@ -1583,11 +1583,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>10:40-10:50</t>
+          <t>10:30-10:40</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66">
@@ -1601,11 +1601,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10:50-11:00</t>
+          <t>10:40-10:50</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
@@ -1619,11 +1619,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11:00-11:10</t>
+          <t>10:50-11:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11:10-11:20</t>
+          <t>11:00-11:10</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69">
@@ -1655,11 +1655,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11:20-11:30</t>
+          <t>11:10-11:20</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
@@ -1673,11 +1673,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11:30-11:40</t>
+          <t>11:20-11:30</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11:40-11:50</t>
+          <t>11:30-11:40</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11:50-12:00</t>
+          <t>11:40-11:50</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73">
@@ -1727,11 +1727,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>12:00-12:10</t>
+          <t>11:50-12:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -1745,11 +1745,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12:10-12:20</t>
+          <t>12:00-12:10</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>12:20-12:30</t>
+          <t>12:10-12:20</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -1781,11 +1781,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12:30-12:40</t>
+          <t>12:20-12:30</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -1799,11 +1799,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>12:40-12:50</t>
+          <t>12:30-12:40</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
@@ -1817,11 +1817,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>12:50-13:00</t>
+          <t>12:40-12:50</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79">
@@ -1835,11 +1835,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>13:00-13:10</t>
+          <t>12:50-13:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
@@ -1853,11 +1853,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>13:10-13:20</t>
+          <t>13:00-13:10</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
@@ -1871,11 +1871,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>13:20-13:30</t>
+          <t>13:10-13:20</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
@@ -1889,11 +1889,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>13:30-13:40</t>
+          <t>13:20-13:30</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>13:40-13:50</t>
+          <t>13:30-13:40</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84">
@@ -1925,11 +1925,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>13:50-14:00</t>
+          <t>13:40-13:50</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>14:00-14:10</t>
+          <t>13:50-14:00</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86">
@@ -1961,11 +1961,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>14:10-14:20</t>
+          <t>14:00-14:10</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87">
@@ -1979,11 +1979,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>14:20-14:30</t>
+          <t>14:10-14:20</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
@@ -1997,11 +1997,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>14:30-14:40</t>
+          <t>14:20-14:30</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>14:40-14:50</t>
+          <t>14:30-14:40</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90">
@@ -2033,11 +2033,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>14:50-15:00</t>
+          <t>14:40-14:50</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -2051,11 +2051,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>15:00-15:10</t>
+          <t>14:50-15:00</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -2069,11 +2069,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>15:10-15:20</t>
+          <t>15:00-15:10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -2087,11 +2087,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>15:20-15:30</t>
+          <t>15:10-15:20</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
@@ -2105,11 +2105,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>15:30-15:40</t>
+          <t>15:20-15:30</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95">
@@ -2123,11 +2123,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>15:40-15:50</t>
+          <t>15:30-15:40</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>15:50-16:00</t>
+          <t>15:40-15:50</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>16:00-16:10</t>
+          <t>15:50-16:00</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98">
@@ -2177,11 +2177,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>16:10-16:20</t>
+          <t>16:00-16:10</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99">
@@ -2195,11 +2195,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>16:20-16:30</t>
+          <t>16:10-16:20</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100">
@@ -2213,11 +2213,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>16:30-16:40</t>
+          <t>16:20-16:30</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
@@ -2231,11 +2231,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>16:40-16:50</t>
+          <t>16:30-16:40</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -2249,11 +2249,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>16:50-17:00</t>
+          <t>16:40-16:50</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>17:00-17:10</t>
+          <t>16:50-17:00</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104">
@@ -2285,11 +2285,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>17:10-17:20</t>
+          <t>17:00-17:10</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105">
@@ -2303,11 +2303,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>17:20-17:30</t>
+          <t>17:10-17:20</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>17:30-17:40</t>
+          <t>17:20-17:30</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107">
@@ -2339,11 +2339,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>17:40-17:50</t>
+          <t>17:30-17:40</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>17:50-18:00</t>
+          <t>17:40-17:50</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109">
@@ -2375,11 +2375,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>18:00-18:10</t>
+          <t>17:50-18:00</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110">
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>18:10-18:20</t>
+          <t>18:00-18:10</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111">
@@ -2411,11 +2411,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>18:20-18:30</t>
+          <t>18:10-18:20</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
@@ -2429,11 +2429,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>18:30-18:40</t>
+          <t>18:20-18:30</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113">
@@ -2447,11 +2447,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>18:40-18:50</t>
+          <t>18:30-18:40</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114">
@@ -2465,11 +2465,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>18:50-19:00</t>
+          <t>18:40-18:50</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115">
@@ -2483,11 +2483,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>19:00-19:10</t>
+          <t>18:50-19:00</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116">
@@ -2501,11 +2501,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>19:10-19:20</t>
+          <t>19:00-19:10</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>19:20-19:30</t>
+          <t>19:10-19:20</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118">
@@ -2537,11 +2537,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>19:30-19:40</t>
+          <t>19:20-19:30</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119">
@@ -2555,11 +2555,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>19:40-19:50</t>
+          <t>19:30-19:40</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120">
@@ -2573,11 +2573,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>19:50-20:00</t>
+          <t>19:40-19:50</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121">
@@ -2591,11 +2591,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20:00-20:10</t>
+          <t>19:50-20:00</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122">
@@ -2609,11 +2609,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20:10-20:20</t>
+          <t>20:00-20:10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>20:20-20:30</t>
+          <t>20:10-20:20</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124">
@@ -2645,11 +2645,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>20:30-20:40</t>
+          <t>20:20-20:30</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125">
@@ -2663,11 +2663,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20:40-20:50</t>
+          <t>20:30-20:40</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126">
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20:50-21:00</t>
+          <t>20:40-20:50</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127">
@@ -2699,11 +2699,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>21:00-21:10</t>
+          <t>20:50-21:00</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128">
@@ -2717,11 +2717,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>21:10-21:20</t>
+          <t>21:00-21:10</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129">
@@ -2735,11 +2735,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>21:20-21:30</t>
+          <t>21:10-21:20</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130">
@@ -2753,11 +2753,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>21:30-21:40</t>
+          <t>21:20-21:30</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>21:40-21:50</t>
+          <t>21:30-21:40</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132">
@@ -2789,11 +2789,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>21:50-22:00</t>
+          <t>21:40-21:50</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133">
@@ -2807,11 +2807,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>22:00-22:10</t>
+          <t>21:50-22:00</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134">
@@ -2825,11 +2825,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>22:10-22:20</t>
+          <t>22:00-22:10</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135">
@@ -2843,11 +2843,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>22:20-22:30</t>
+          <t>22:10-22:20</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136">
@@ -2861,11 +2861,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>22:30-22:40</t>
+          <t>22:20-22:30</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137">
@@ -2879,11 +2879,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>22:40-22:50</t>
+          <t>22:30-22:40</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138">
@@ -2897,11 +2897,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>22:50-23:00</t>
+          <t>22:40-22:50</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139">
@@ -2915,11 +2915,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>23:00-23:10</t>
+          <t>22:50-23:00</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>23:10-23:20</t>
+          <t>23:00-23:10</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141">
@@ -2951,11 +2951,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>23:20-23:30</t>
+          <t>23:10-23:20</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142">
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>23:30-23:40</t>
+          <t>23:20-23:30</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="143">
@@ -2987,11 +2987,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>23:40-23:50</t>
+          <t>23:30-23:40</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="144">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>23:50-0:00+1</t>
+          <t>23:40-23:50</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="145">
@@ -3023,11 +3023,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>0:00-0:10+1</t>
+          <t>23:50-0:00+1</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
